--- a/Employee_Reports_wi48/Mario Dorado Hernandez Q0446.xlsx
+++ b/Employee_Reports_wi48/Mario Dorado Hernandez Q0446.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1042,9 +1042,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>11-Jun-2026</t>
@@ -1056,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1105,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1154,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1203,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1240,11 +1252,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
